--- a/03_bloques/B03/B03_trabajo.xlsx
+++ b/03_bloques/B03/B03_trabajo.xlsx
@@ -587,7 +587,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1171,7 +1171,7 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1849,7 +1849,7 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2092,7 +2092,7 @@
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2386,7 +2386,7 @@
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2974,7 +2974,7 @@
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3758,7 +3758,7 @@
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4099,7 +4099,7 @@
       <c r="G74" s="3" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4346,7 +4346,7 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4393,7 +4393,7 @@
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4683,7 +4683,7 @@
       <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4973,7 +4973,7 @@
       <c r="G92" s="3" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5263,7 +5263,7 @@
       <c r="G98" s="3" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       <c r="G101" s="3" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       <c r="G102" s="3" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       <c r="G105" s="3" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5706,7 +5706,7 @@
       <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       <c r="G110" s="3" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -6000,7 +6000,7 @@
       <c r="G113" s="3" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       <c r="G124" s="5" t="inlineStr"/>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
@@ -6588,7 +6588,7 @@
       <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       <c r="G126" s="3" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -6882,7 +6882,7 @@
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       <c r="G132" s="3" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
@@ -7027,7 +7027,7 @@
       <c r="G134" s="5" t="inlineStr"/>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
@@ -7176,7 +7176,7 @@
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -7470,7 +7470,7 @@
       <c r="G143" s="5" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7568,7 +7568,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       <c r="G146" s="3" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -7713,7 +7713,7 @@
       <c r="G148" s="5" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -7862,7 +7862,7 @@
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       <c r="G152" s="3" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       <c r="G156" s="3" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       <c r="G157" s="3" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       <c r="G161" s="3" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       <c r="G164" s="5" t="inlineStr"/>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
@@ -8552,7 +8552,7 @@
       <c r="G165" s="3" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       <c r="G167" s="3" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       <c r="G170" s="3" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       <c r="G173" s="3" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       <c r="G177" s="5" t="inlineStr"/>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
@@ -9195,7 +9195,7 @@
       <c r="G178" s="3" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
       <c r="G180" s="3" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       <c r="G181" s="5" t="inlineStr"/>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -9438,7 +9438,7 @@
       <c r="G183" s="3" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -9536,7 +9536,7 @@
       <c r="G185" s="5" t="inlineStr"/>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
@@ -9583,7 +9583,7 @@
       <c r="G186" s="3" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       <c r="G189" s="5" t="inlineStr"/>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
@@ -9826,7 +9826,7 @@
       <c r="G191" s="3" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       <c r="G193" s="5" t="inlineStr"/>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I193" s="4" t="inlineStr">
@@ -10022,7 +10022,7 @@
       <c r="G195" s="3" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -10069,7 +10069,7 @@
       <c r="G196" s="5" t="inlineStr"/>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I196" s="4" t="inlineStr">
@@ -10116,7 +10116,7 @@
       <c r="G197" s="3" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       <c r="G199" s="5" t="inlineStr"/>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I199" s="4" t="inlineStr">
@@ -10312,7 +10312,7 @@
       <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -10331,7 +10331,7 @@
   <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Borrador,Sin borrador,Revisar_Juan,Enviado,Validado,Grabado"</formula1>
+      <formula1>"Borrador,Sin borrador,Por_revisar,Enviado,Validado,Grabado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -10435,7 +10435,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -26120,7 +26120,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Español redactado o adaptado por Claude (Revisar_Juan)</t>
+          <t>Español redactado o adaptado por Claude (Por_revisar)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
